--- a/web/files/港岛-半山区西部-宝峰.xlsx
+++ b/web/files/港岛-半山区西部-宝峰.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>6799</v>
+        <v>6668</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -829,14 +829,14 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
         <v>399000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>58685</v>
+        <v>59838</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1927,10 +1927,10 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 6799呎 (4+房)
+          <t>A | 6668呎 (4+房)
 $39900万
-$58,685/呎
-(26年-09月-03日)</t>
+$59,838/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-宝峰.xlsx
+++ b/web/files/港岛-半山区西部-宝峰.xlsx
@@ -121,7 +121,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -266,7 +267,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -820,7 +821,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>6668</v>
+        <v>6799</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -836,7 +837,7 @@
         <v>399000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>59838</v>
+        <v>58685</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -890,7 +891,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -900,12 +901,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -915,12 +916,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -930,7 +931,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1862,27 +1863,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -1927,9 +1928,9 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 6668呎 (4+房)
+          <t>A | 6799呎 (4+房)
 $39900万
-$59,838/呎
+$58,685/呎
 (26年-09月-21日)</t>
         </is>
       </c>
@@ -1944,9 +1945,9 @@
       <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 7263呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
